--- a/resources/templates/Template_F24_Configura_AI_v1.0.xlsx
+++ b/resources/templates/Template_F24_Configura_AI_v1.0.xlsx
@@ -795,8 +795,16 @@
           <t>ABC123</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>

--- a/resources/templates/Template_F24_Configura_AI_v1.0.xlsx
+++ b/resources/templates/Template_F24_Configura_AI_v1.0.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="PAGAMENTI" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ISTRUZIONI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ESEMPI_NON_IMPORTARE" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PAGAMENTI'!$A$1:$AH$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PAGAMENTI'!$A$1:$AH$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,15 +31,16 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="008D2320"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -50,7 +52,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00145368"/>
+        <fgColor rgb="00EFEDE8"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,15 +68,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH6"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -456,8 +463,8 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
@@ -472,7 +479,7 @@
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="20" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="32" customWidth="1" min="29" max="29"/>
+    <col width="34" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="25" customWidth="1" min="31" max="31"/>
     <col width="29" customWidth="1" min="32" max="32"/>
@@ -652,426 +659,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ALFA S.R.L.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>01234567897</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>01234567897</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Dipendenti</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>16/09/2026</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Erario</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0008</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Ritenute lavoro dipendente</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ALFA S.R.L.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>01234567897</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>01234567897</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Dipendenti</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>16/09/2026</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>INPS</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>DM10</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>28000</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>ABC123</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>08/2026</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>08/2026</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Contributi dipendenti</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ALFA S.R.L.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>01234567897</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>01234567897</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Autonomi</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>16/09/2026</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Erario</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1040</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0008</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>5500</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Ritenute lavoro autonomo</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ALFA S.R.L.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>01234567897</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>01234567897</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Autonomi</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>16/09/2026</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Erario</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>6099</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Credito IVA in compensazione</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BETA S.P.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>09876543217</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>09876543217</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Dipendenti</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>16/09/2026</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Erario</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0008</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>9000</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Ritenute lavoro dipendente</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AH6"/>
+  <autoFilter ref="A1:AH1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1082,11 +671,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="108" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1095,21 +684,23 @@
           <t>TAX AUTOMATION LAB — TEMPLATE F24 PER LA CONFIGURAZIONE CON AI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Regola</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Indicazione</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Identificazione della societa</t>
         </is>
@@ -1121,7 +712,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Flusso</t>
         </is>
@@ -1133,7 +724,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Periodo / rateazione</t>
         </is>
@@ -1145,7 +736,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Importi</t>
         </is>
@@ -1157,7 +748,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Campi specifici</t>
         </is>
@@ -1169,7 +760,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Codice tributo</t>
         </is>
@@ -1181,7 +772,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Compensazioni</t>
         </is>
@@ -1193,7 +784,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Capienza del modello</t>
         </is>
@@ -1205,7 +796,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Nessun identificativo interno</t>
         </is>
@@ -1217,18 +808,596 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Righe di esempio</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Foglio PAGAMENTI</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Le cinque righe del foglio PAGAMENTI sono un esempio funzionante: cancellale prima di inserire i dati veri.</t>
+          <t>Esce vuoto, con le sole intestazioni. Compilalo con i dati del tuo cliente. Se lo ricarichi intatto il tool risponde "nessun pagamento da importare": e corretto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Foglio ESEMPI_NON_IMPORTARE</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Contiene righe di esempio su societa inventate (ALFA S.R.L. e BETA S.P.A.). Il tool non legge questo foglio. Non copiare quelle righe in PAGAMENTI: le riconosce e le esclude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Riconciliazione</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Prima di importare, confronta il numero di righe compilate in PAGAMENTI con i documenti da cui provengono. Il tool dichiara quante righe ha letto: i due numeri devono coincidere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Dato ambiguo</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Se una fonte non distingue debito e credito, lascia vuote entrambe le colonne e annota il dubbio: non indovinare il segno.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="34" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="25" customWidth="1" min="31" max="31"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>ESEMPI - NON IMPORTATI. Questo foglio mostra come si compila una riga. Il tool importa il foglio PAGAMENTI: copia li i tuoi dati, non questi. ALFA S.R.L. e BETA S.P.A. sono societa inventate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Denominazione</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Codice fiscale</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Partita IVA</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Flusso</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Descrizione flusso</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Data pagamento</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Sezione</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Codice tributo / causale</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Periodo / rateazione</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Anno</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Importo debito</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>Importo credito</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>Codice ente / sede / regione / comune</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>Matricola / posizione / riferimento</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>Periodo da</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>Periodo a</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>Codice ufficio</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>Codice atto</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>Ravvedimento</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>Immobili variati</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>Acconto</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>Saldo</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>Numero immobili</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>Detrazione</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>Codice ditta INAIL</t>
+        </is>
+      </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>C.C. INAIL</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>Codice posizione</t>
+        </is>
+      </c>
+      <c r="AB2" s="1" t="inlineStr">
+        <is>
+          <t>CF coobbligato</t>
+        </is>
+      </c>
+      <c r="AC2" s="1" t="inlineStr">
+        <is>
+          <t>Codice identificativo coobbligato</t>
+        </is>
+      </c>
+      <c r="AD2" s="1" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+      <c r="AE2" s="1" t="inlineStr">
+        <is>
+          <t>Numero certificazione</t>
+        </is>
+      </c>
+      <c r="AF2" s="1" t="inlineStr">
+        <is>
+          <t>Identificativo operazione</t>
+        </is>
+      </c>
+      <c r="AG2" s="1" t="inlineStr">
+        <is>
+          <t>Codice ente previdenziale</t>
+        </is>
+      </c>
+      <c r="AH2" s="1" t="inlineStr">
+        <is>
+          <t>Anno imposta non coincidente</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ALFA S.R.L.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01234567897</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>01234567897</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Dipendenti</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Erario</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0008</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Ritenute lavoro dipendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ALFA S.R.L.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>01234567897</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01234567897</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Dipendenti</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>INPS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DM10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>28000</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Contributi dipendenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ALFA S.R.L.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01234567897</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>01234567897</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Autonomi</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Erario</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0008</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>5500</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Ritenute lavoro autonomo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ALFA S.R.L.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01234567897</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>01234567897</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Autonomi</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Erario</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6099</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Credito IVA in compensazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BETA S.P.A.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09876543217</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>09876543217</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Dipendenti</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Erario</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0008</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Ritenute lavoro dipendente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>